--- a/viewer/downloads/CC2_Alignment.xlsx
+++ b/viewer/downloads/CC2_Alignment.xlsx
@@ -742,12 +742,12 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.SP.5 (CCSS-M), 7.SP.6 (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.5 (CCSS-M), 7.SP.C.6 (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.5 (CCSS-M), 7.SP.6 (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.5 (CCSS-M), 7.SP.C.6 (CCSS-M)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.SP.6 (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.6 (CCSS-M), 7.SP.C.7.B (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.6 (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.6 (CCSS-M), 7.SP.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.3 (MN-2022), 7.SP.8a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.8 (CCSS-M)</t>
+          <t>7.1.2.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.3 (MN-2022), 7.SP.8a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.8.A (CCSS-M)</t>
+          <t>7.1.2.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.8.A (CCSS-M)</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.3.5.1 (MN-2022), 7.NS.2d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2007), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.1 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.NS.2d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.3.5.1 (MN-2022), 7.NS.2d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2007), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.1 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.NS.2d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.5 (MN-2022), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.5 (MN-2022), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.2 (MN-2022), 7.3.5.6 (MN-2022), 7.NS.1a (CCSS-M), 7.NS.1b (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.A (CCSS-M), 7.NS.A.1.B (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.2 (MN-2022), 7.3.5.6 (MN-2022), 7.NS.1a (CCSS-M), 7.NS.1b (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.A (CCSS-M), 7.NS.A.1.B (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.2 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.NS.1a (CCSS-M), 7.NS.1b (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.A (CCSS-M), 7.NS.A.1.B (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.2 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.NS.1a (CCSS-M), 7.NS.1b (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.A (CCSS-M), 7.NS.A.1.B (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.2 (MN-2022), 7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.2 (MN-2022), 7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.6 (MN-2022), 7.NS.1d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.NS.1d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>7.3.6.3 (MN-2022), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.3 (MN-2022), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.6.3 (MN-2022), 7.NS.1c (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.C (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.6.3 (MN-2022), 7.NS.1c (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.C (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.4 (MN-2022), 7.NS.2a (CCSS-M), 7.NS.2b (CCSS-M), 7.NS.2c (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.4 (MN-2022), 7.NS.2a (CCSS-M), 7.NS.2b (CCSS-M), 7.NS.2c (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.5 (MN-2022), 7.3.6.5 (MN-2022), 7.NS.3 (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.5 (MN-2022), 7.3.6.5 (MN-2022), 7.NS.3 (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>7.3.6.5 (MN-2022), 7.NS.2b (CCSS-M), 7.NS.3 (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.5 (MN-2022), 7.NS.2b (CCSS-M), 7.NS.3 (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.6 (MN-2022), 7.3.6.5 (MN-2022), 7.NS.1d (CCSS-M), 7.NS.2c (CCSS-M), 7.NS.3 (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.5 (MN-2022), 7.NS.1d (CCSS-M), 7.NS.2c (CCSS-M), 7.NS.3 (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.2 (MN-2022), 7.2.4.4 (MN-2022), 7.3.5.7 (MN-2022), 7.G.1 (CCSS-M), 7.G.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.2.4.2 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.3.5.7 (MN-2022), 7.G.1 (CCSS-M), 7.G.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.2 (MN-2022), 7.2.4.4 (MN-2022), 7.G.1 (CCSS-M), 7.G.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.4.2 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.1 (CCSS-M), 7.G.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>7.3.7.2 (MN-2022), 7.RP.2a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.7.2 (MN-2022), 7.RP.2a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1825,12 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>7.3.7.1 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.7.1 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.7 (MN-2022), 7.RP.1 (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.A.1 (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.7 (MN-2022), 7.RP.1 (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.A.1 (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1895,12 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>7.3.6.1 (MN-2022), 7.EE.1 (CCSS-M), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.1 (MN-2022), 7.EE.1 (CCSS-M), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>7.3.6.1 (MN-2022), 7.EE.1 (CCSS-M), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.1 (MN-2022), 7.EE.1 (CCSS-M), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2023,12 @@
       <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.5.7 (MN-2022)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.3.5.7 (MN-2022)</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.5 (MN-2022), 7.3.6.4 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.5 (MN-2022), 7.3.6.4 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M)</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.5 (MN-2022), 7.3.6.4 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.5 (MN-2022), 7.3.6.4 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M)</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.5 (MN-2022), 7.1.2.6 (MN-2022), 7.RP.2b (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.7c (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.5 (MN-2022), 7.1.2.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.7c (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.3 (MN-2022), 7.RP.2b (CCSS-M), 7.SP.6 (CCSS-M)</t>
+          <t>7.1.2.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.6 (CCSS-M)</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.4 (MN-2022), 7.1.2.6 (MN-2022), 7.RP.2b (CCSS-M), 7.SP.8b (CCSS-M)</t>
+          <t>7.1.2.4 (MN-2022), 7.1.2.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8b (CCSS-M)</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -2277,12 +2277,12 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.4 (MN-2022), 7.1.2.6 (MN-2022), 7.RP.2b (CCSS-M), 7.SP.8a (CCSS-M), 7.Sp.8a (CCSS-M)</t>
+          <t>7.1.2.4 (MN-2022), 7.1.2.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8a (CCSS-M), 7.Sp.8a (CCSS-M)</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.3 (MN-2022), 7.RP.2b (CCSS-M), 7.SP.8a (CCSS-M), 7.SP.8b (CCSS-M)</t>
+          <t>7.1.2.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8a (CCSS-M), 7.SP.8b (CCSS-M)</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2515,12 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.1 (MN-2022), 7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.4.1 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.1 (MN-2022), 7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.4.1 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.1 (MN-2022), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.4.1 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2978,12 +2978,12 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.3 (MN-2022), 7.3.6.2 (MN-2022), 7.NS.3 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.3 (MN-2022), 7.3.6.2 (MN-2022), 7.NS.3 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3137,12 +3137,12 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>7.3.6.2 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.2 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3216,12 +3216,12 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>7.2.1 (CCSS-M), 7.3.6.2 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.RP.2b (CCSS-M), 7.SP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1 (CCSS-M), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.2 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.RP.2b (CCSS-M), 7.SP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.RP.2b (CCSS-M), 7.SP.1 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.1 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.3.6.4 (MN-2022), 7.RP.2b (CCSS-M), 7.SP.2 (CCSS-M), 7.SP.4 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.4 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.2 (CCSS-M), 7.SP.4 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -3706,12 +3706,12 @@
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.4 (MN-2022), 7.1.1.5 (MN-2022), see ebook (CCSS-M)</t>
+          <t>7.1.1.4 (MN-2022), 7.1.1.5 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3776,12 +3776,12 @@
       <c r="E109" s="7" t="inlineStr"/>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.5 (MN-2022)</t>
+          <t>7.1.1.5 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007)</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       <c r="E110" s="7" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022)</t>
+          <t>7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007)</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       <c r="E111" s="7" t="inlineStr"/>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.4 (MN-2022)</t>
+          <t>7.2.3.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007)</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3870,12 +3870,12 @@
       <c r="E113" s="7" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022)</t>
+          <t>7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007)</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_mn2022, mn_correlation_supplement</t>
         </is>
       </c>
     </row>

--- a/viewer/downloads/CC2_Alignment.xlsx
+++ b/viewer/downloads/CC2_Alignment.xlsx
@@ -614,12 +614,12 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>7.SP.8c (CCSS-M), 7.SP.C.6 (CCSS-M), 7.SP.C.8.C (CCSS-M)</t>
+          <t>7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8c (CCSS-M), 7.SP.C.6 (CCSS-M), 7.SP.C.8.C (CCSS-M)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -645,12 +645,12 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>7.SP.8c (CCSS-M), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.SP.8c (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>7.RP.A.2 (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.RP.A.2 (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -707,12 +707,12 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -742,12 +742,12 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.5 (CCSS-M), 7.SP.6 (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.5 (CCSS-M), 7.SP.C.6 (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.5 (CCSS-M), 7.SP.6 (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.5 (CCSS-M), 7.SP.C.6 (CCSS-M)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.6 (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.6 (CCSS-M), 7.SP.C.7.B (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.6 (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.6 (CCSS-M), 7.SP.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>7.SP.7a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.7.A (CCSS-M)</t>
+          <t>7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.7a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.7.A (CCSS-M)</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>6.RP.A.3 (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>6.1.2.1 (MN-2007), 6.1.2.2 (MN-2007), 6.1.2.3 (MN-2007), 6.RP.A.3 (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.8 (CCSS-M)</t>
+          <t>7.1.2.3 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.8.A (CCSS-M)</t>
+          <t>7.1.2.3 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.8.A (CCSS-M)</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2007), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.1 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.NS.2d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2007), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2007), 7.3.5.1 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.NS.2d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2007), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.1 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.NS.2d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2007), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2007), 7.3.5.1 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.NS.2d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.5 (MN-2022), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.5 (MN-2022), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.2 (MN-2022), 7.3.5.6 (MN-2022), 7.NS.1a (CCSS-M), 7.NS.1b (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.A (CCSS-M), 7.NS.A.1.B (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.2 (MN-2022), 7.3.5.6 (MN-2022), 7.NS.1a (CCSS-M), 7.NS.1b (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.A (CCSS-M), 7.NS.A.1.B (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.2 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.NS.1a (CCSS-M), 7.NS.1b (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.A (CCSS-M), 7.NS.A.1.B (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.2 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.NS.1a (CCSS-M), 7.NS.1b (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.A (CCSS-M), 7.NS.A.1.B (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.2 (MN-2022), 7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.2 (MN-2022), 7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>7.NS.2a (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.NS.2a (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.NS.1d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.6 (MN-2022), 7.NS.1d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.3 (MN-2022), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.6.3 (MN-2022), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.6.3 (MN-2022), 7.NS.1c (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.C (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.6.3 (MN-2022), 7.NS.1c (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.C (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>7.NS.1c (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.C (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.NS.1c (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.C (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.4 (MN-2022), 7.NS.2a (CCSS-M), 7.NS.2b (CCSS-M), 7.NS.2c (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.4 (MN-2022), 7.NS.2a (CCSS-M), 7.NS.2b (CCSS-M), 7.NS.2c (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.5 (MN-2022), 7.3.6.5 (MN-2022), 7.NS.3 (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.5 (MN-2022), 7.3.6.5 (MN-2022), 7.NS.3 (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.5 (MN-2022), 7.NS.2b (CCSS-M), 7.NS.3 (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.6.5 (MN-2022), 7.NS.2b (CCSS-M), 7.NS.3 (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.5 (MN-2022), 7.NS.1d (CCSS-M), 7.NS.2c (CCSS-M), 7.NS.3 (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.5 (MN-2022), 7.NS.1d (CCSS-M), 7.NS.2c (CCSS-M), 7.NS.3 (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.2.4.2 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.3.5.7 (MN-2022), 7.G.1 (CCSS-M), 7.G.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.4.2 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.5.7 (MN-2022), 7.G.1 (CCSS-M), 7.G.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.2 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.1 (CCSS-M), 7.G.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.4.2 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.G.1 (CCSS-M), 7.G.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.7.2 (MN-2022), 7.RP.2a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.7.2 (MN-2022), 7.RP.2a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1825,12 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.7.1 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.7.1 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.7 (MN-2022), 7.RP.1 (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.A.1 (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.5.7 (MN-2022), 7.RP.1 (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.A.1 (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1895,12 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.1 (MN-2022), 7.EE.1 (CCSS-M), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.1 (MN-2022), 7.EE.1 (CCSS-M), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1961,12 +1961,12 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.1 (MN-2022), 7.EE.1 (CCSS-M), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.1 (MN-2022), 7.EE.1 (CCSS-M), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2023,12 @@
       <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.3.5.7 (MN-2022)</t>
+          <t>7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.5.7 (MN-2022)</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.5 (MN-2022), 7.3.6.4 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M)</t>
+          <t>7.3.5.5 (MN-2022), 7.3.6.4 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M)</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.5 (MN-2022), 7.3.6.4 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M)</t>
+          <t>7.3.5.5 (MN-2022), 7.3.6.4 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M)</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.5 (MN-2022), 7.1.2.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.7c (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.5 (MN-2022), 7.1.2.6 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.7c (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.6 (CCSS-M)</t>
+          <t>7.1.2.3 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.6 (CCSS-M)</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.4 (MN-2022), 7.1.2.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8b (CCSS-M)</t>
+          <t>7.1.2.4 (MN-2022), 7.1.2.6 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8b (CCSS-M)</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.4 (MN-2022), 7.1.2.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8a (CCSS-M), 7.Sp.8a (CCSS-M)</t>
+          <t>7.1.2.4 (MN-2022), 7.1.2.6 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8a (CCSS-M), 7.Sp.8a (CCSS-M)</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8a (CCSS-M), 7.SP.8b (CCSS-M)</t>
+          <t>7.1.2.3 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8a (CCSS-M), 7.SP.8b (CCSS-M)</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.1 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.4.1 (MN-2022), 7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.1 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.4.1 (MN-2022), 7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.1 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.4.1 (MN-2022), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.3.5.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2978,12 +2978,12 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.3 (MN-2022), 7.3.6.2 (MN-2022), 7.NS.3 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.3.5.3 (MN-2022), 7.3.6.2 (MN-2022), 7.NS.3 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3137,12 +3137,12 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.2 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.3.6.2 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3216,12 +3216,12 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1 (CCSS-M), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.2 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.RP.2b (CCSS-M), 7.SP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.1 (CCSS-M), 7.3.6.2 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.RP.2b (CCSS-M), 7.SP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.1 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.1 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.4 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.2 (CCSS-M), 7.SP.4 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.3.6.4 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.2 (CCSS-M), 7.SP.4 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.4 (MN-2022), 7.1.1.5 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), see ebook (CCSS-M)</t>
+          <t>7.1.1.4 (MN-2022), 7.1.1.5 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -3776,7 +3776,7 @@
       <c r="E109" s="7" t="inlineStr"/>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.5 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007)</t>
+          <t>7.1.1.5 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007)</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -3803,12 +3803,12 @@
       <c r="E110" s="7" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007)</t>
+          <t>7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022)</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       <c r="E111" s="7" t="inlineStr"/>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007)</t>
+          <t>7.2.3.4 (MN-2022)</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, mn_correlation</t>
+          <t>mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       <c r="E113" s="7" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007)</t>
+          <t>7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007)</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">

--- a/viewer/downloads/CC2_Alignment.xlsx
+++ b/viewer/downloads/CC2_Alignment.xlsx
@@ -742,12 +742,12 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.5 (CCSS-M), 7.SP.6 (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.5 (CCSS-M), 7.SP.C.6 (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.5 (CCSS-M), 7.SP.6 (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.5 (CCSS-M), 7.SP.C.6 (CCSS-M)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.6 (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.6 (CCSS-M), 7.SP.C.7.B (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.6 (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.6 (CCSS-M), 7.SP.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>7.SP.8c (CCSS-M), Prep for 7.SP.C.8.A (CCSS-M)</t>
+          <t>7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8c (CCSS-M), Prep for 7.SP.C.8.A (CCSS-M)</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.3 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.8 (CCSS-M)</t>
+          <t>7.1.2.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.8 (CCSS-M)</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.3 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.8.A (CCSS-M)</t>
+          <t>7.1.2.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.8.A (CCSS-M)</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2007), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2007), 7.3.5.1 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.NS.2d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2007), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2007), 7.3.5.1 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.NS.2d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2007), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2007), 7.3.5.1 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.NS.2d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2007), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2007), 7.3.5.1 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.NS.2d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.5 (MN-2022), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.5.5 (MN-2022), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.2 (MN-2022), 7.3.5.6 (MN-2022), 7.NS.1a (CCSS-M), 7.NS.1b (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.A (CCSS-M), 7.NS.A.1.B (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.2 (MN-2022), 7.3.5.6 (MN-2022), 7.NS.1a (CCSS-M), 7.NS.1b (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.A (CCSS-M), 7.NS.A.1.B (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.2 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.NS.1a (CCSS-M), 7.NS.1b (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.A (CCSS-M), 7.NS.A.1.B (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.2 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.NS.1a (CCSS-M), 7.NS.1b (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.A (CCSS-M), 7.NS.A.1.B (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.2 (MN-2022), 7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.2 (MN-2022), 7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.6 (MN-2022), 7.NS.1d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.5.6 (MN-2022), 7.NS.1d (CCSS-M), 7.NS.A.2.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.6.3 (MN-2022), 7.NS.1c (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.C (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.6.3 (MN-2022), 7.NS.1c (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.C (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.5 (MN-2022), 7.3.6.5 (MN-2022), 7.NS.3 (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.5.5 (MN-2022), 7.3.6.5 (MN-2022), 7.NS.3 (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.6.5 (MN-2022), 7.NS.2b (CCSS-M), 7.NS.3 (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.6.5 (MN-2022), 7.NS.2b (CCSS-M), 7.NS.3 (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.5 (MN-2022), 7.NS.1d (CCSS-M), 7.NS.2c (CCSS-M), 7.NS.3 (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.5 (MN-2022), 7.NS.1d (CCSS-M), 7.NS.2c (CCSS-M), 7.NS.3 (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.2 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.5.7 (MN-2022), 7.G.1 (CCSS-M), 7.G.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.4.2 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.3.5.7 (MN-2022), 7.G.1 (CCSS-M), 7.G.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.2 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.G.1 (CCSS-M), 7.G.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.4.2 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.1 (CCSS-M), 7.G.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.7.2 (MN-2022), 7.RP.2a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.7.2 (MN-2022), 7.RP.2a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.7.1 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.7.1 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.5.7 (MN-2022), 7.RP.1 (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.A.1 (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.5.7 (MN-2022), 7.RP.1 (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.A.1 (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M), 7.RP.A.2.C (CCSS-M), 7.RP.A.2.D (CCSS-M)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.1 (MN-2022), 7.EE.1 (CCSS-M), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.1 (MN-2022), 7.EE.1 (CCSS-M), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.1 (MN-2022), 7.EE.1 (CCSS-M), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.1 (MN-2022), 7.EE.1 (CCSS-M), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2023,12 @@
       <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.5.7 (MN-2022)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.3.5.7 (MN-2022)</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.5 (MN-2022), 7.3.6.4 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.5.5 (MN-2022), 7.3.6.4 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M)</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.5 (MN-2022), 7.3.6.4 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.5.5 (MN-2022), 7.3.6.4 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M)</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.5 (MN-2022), 7.1.2.6 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.7c (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.5 (MN-2022), 7.1.2.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.7b (CCSS-M), 7.SP.7c (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.3 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.6 (CCSS-M)</t>
+          <t>7.1.2.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.6 (CCSS-M)</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.4 (MN-2022), 7.1.2.6 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8b (CCSS-M)</t>
+          <t>7.1.2.4 (MN-2022), 7.1.2.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8b (CCSS-M)</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.4 (MN-2022), 7.1.2.6 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8a (CCSS-M), 7.Sp.8a (CCSS-M)</t>
+          <t>7.1.2.4 (MN-2022), 7.1.2.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8a (CCSS-M), 7.Sp.8a (CCSS-M)</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.3 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8a (CCSS-M), 7.SP.8b (CCSS-M)</t>
+          <t>7.1.2.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.8a (CCSS-M), 7.SP.8b (CCSS-M)</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2467,12 +2467,12 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2515,12 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.1 (MN-2022), 7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.4.1 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.1 (MN-2022), 7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.4.1 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>7.2.4.1 (MN-2022), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.2.4.1 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2771,12 +2771,12 @@
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.5.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.2c (CCSS-M), 7.RP.2d (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -2943,12 +2943,12 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>7.NS.3 (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.NS.3 (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2978,12 +2978,12 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>7.3.5.3 (MN-2022), 7.3.6.2 (MN-2022), 7.NS.3 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.3 (MN-2022), 7.3.6.2 (MN-2022), 7.NS.3 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3137,12 +3137,12 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>7.3.6.2 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.2 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3168,12 +3168,12 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3216,12 +3216,12 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>7.2.1 (CCSS-M), 7.3.6.2 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.RP.2b (CCSS-M), 7.SP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.1 (CCSS-M), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.6.2 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>7.RP.2b (CCSS-M), 7.SP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.1 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.1 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.3.6.4 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.2 (CCSS-M), 7.SP.4 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.3.6.4 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.2 (CCSS-M), 7.SP.4 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation, mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_mn2022, ccss_lesson_guide, ccss_pdf_correlation, mn_correlation, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -3485,12 +3485,12 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>7.2.1 (CCSS-M), 7.G.4 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.1 (CCSS-M), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.4 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>7.G.4 (CCSS-M), 7.G.6 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.4 (CCSS-M), 7.G.6 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>7.2.1 (CCSS-M), 7.G.3 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.1 (CCSS-M), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.3 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3644,12 +3644,12 @@
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>7.G.6 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.6 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>7.G.6 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.6 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_ccss, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.4 (MN-2022), 7.1.1.5 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), see ebook (CCSS-M)</t>
+          <t>7.1.1.4 (MN-2022), 7.1.1.5 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -3776,7 +3776,7 @@
       <c r="E109" s="7" t="inlineStr"/>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.5 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007)</t>
+          <t>7.1.1.5 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007)</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -3803,12 +3803,12 @@
       <c r="E110" s="7" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022)</t>
+          <t>7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007)</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       <c r="E111" s="7" t="inlineStr"/>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.4 (MN-2022)</t>
+          <t>7.2.3.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007)</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_mn2022, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       <c r="E113" s="7" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007)</t>
+          <t>7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007)</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">

--- a/viewer/downloads/CC2_Alignment.xlsx
+++ b/viewer/downloads/CC2_Alignment.xlsx
@@ -497,7 +497,7 @@
     <col width="55" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
@@ -606,7 +606,11 @@
           <t>Probability</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>7.1.1.1, 7.1.1.2, 7.1.1.3, 7.1.1.4, 7.1.1.5, 7.1.1.6, 7.1.2.1, 7.1.2.2, 7.1.2.3, 7.1.2.4, 7.1.2.5, 7.1.2.6</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
           <t>7.SP.8c, 7.SP.C.6, 7.SP.C.8.C</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8c (CCSS-M), 7.SP.C.6 (CCSS-M), 7.SP.C.8.C (CCSS-M)</t>
+          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.4 (MN-2022), 7.1.1.5 (MN-2022), 7.1.1.6 (MN-2022), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2022), 7.1.2.4 (MN-2022), 7.1.2.5 (MN-2022), 7.1.2.6 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8c (CCSS-M), 7.SP.C.6 (CCSS-M), 7.SP.C.8.C (CCSS-M)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -637,7 +641,11 @@
           <t>Variables and Solutions</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>8.3.5.2, 8.3.5.3, 8.3.5.6, 8.3.5.7, 8.3.6.1, 8.3.6.2, 8.3.6.3, 8.3.6.4, 8.3.6.6, 8.3.6.7, 8.3.6.8, 8.3.6.9, 8.3.7.2, 8.3.7.3, 8.3.7.4, 8.3.7.5, 8.3.7.9</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
           <t>7.SP.8c, 8.EE.C.7.B</t>
@@ -645,7 +653,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>7.SP.8c (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.EE.C.7.B (CCSS-M)</t>
+          <t>7.SP.8c (CCSS-M), 8.2.1.1 (MN-2007), 8.2.1.2 (MN-2007), 8.2.3.1 (MN-2007), 8.3.5.2 (MN-2022), 8.3.5.3 (MN-2022), 8.3.5.6 (MN-2022), 8.3.5.7 (MN-2022), 8.3.6.1 (MN-2022), 8.3.6.2 (MN-2022), 8.3.6.3 (MN-2022), 8.3.6.4 (MN-2022), 8.3.6.6 (MN-2022), 8.3.6.7 (MN-2022), 8.3.6.8 (MN-2022), 8.3.6.9 (MN-2022), 8.3.7.2 (MN-2022), 8.3.7.3 (MN-2022), 8.3.7.4 (MN-2022), 8.3.7.5 (MN-2022), 8.3.7.9 (MN-2022), 8.EE.C.7.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -668,7 +676,11 @@
           <t>Proportional Reasoning</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4, 7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>7.RP.A.2, 7.SP.8c</t>
@@ -676,7 +688,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.RP.A.2 (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022), 7.2.4.1 (MN-2022), 7.2.4.2 (MN-2022), 7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.5.1 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.5.7 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.A.2 (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -699,7 +711,11 @@
           <t>Rational numbers and decimals</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
           <t>7.NS.A.2.D, 7.SP.8c</t>
@@ -707,7 +723,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.1 (MN-2022), 7.3.5.2 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.NS.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -800,7 +816,11 @@
           <t>Probability</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>7.1.1.1, 7.1.1.2, 7.1.1.3, 7.1.1.4, 7.1.1.5, 7.1.1.6, 7.1.2.1, 7.1.2.2, 7.1.2.3, 7.1.2.4, 7.1.2.5, 7.1.2.6</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
           <t>7.SP.7a, 7.SP.8c, 7.SP.C.7.A</t>
@@ -808,7 +828,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.7a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.7.A (CCSS-M)</t>
+          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.4 (MN-2022), 7.1.1.5 (MN-2022), 7.1.1.6 (MN-2022), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2022), 7.1.2.4 (MN-2022), 7.1.2.5 (MN-2022), 7.1.2.6 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.7a (CCSS-M), 7.SP.8c (CCSS-M), 7.SP.C.7.A (CCSS-M)</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -831,7 +851,11 @@
           <t>Percent</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr"/>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>6.3.5.10, 6.3.5.11, 6.3.5.2, 6.3.5.3, 6.3.5.6, 6.3.6.1, 6.3.6.2, 6.3.6.3, 6.3.6.4, 6.3.6.5, 6.3.6.6</t>
+        </is>
+      </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
           <t>6.RP.A.3, 7.SP.8c</t>
@@ -839,7 +863,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>6.1.2.1 (MN-2007), 6.1.2.2 (MN-2007), 6.1.2.3 (MN-2007), 6.RP.A.3 (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>6.1.2.1 (MN-2007), 6.1.2.2 (MN-2007), 6.1.2.3 (MN-2007), 6.3.5.10 (MN-2022), 6.3.5.11 (MN-2022), 6.3.5.2 (MN-2022), 6.3.5.3 (MN-2022), 6.3.5.6 (MN-2022), 6.3.6.1 (MN-2022), 6.3.6.2 (MN-2022), 6.3.6.3 (MN-2022), 6.3.6.4 (MN-2022), 6.3.6.5 (MN-2022), 6.3.6.6 (MN-2022), 6.RP.A.3 (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -862,7 +886,11 @@
           <t>Probability</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr"/>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>7.1.1.1, 7.1.1.2, 7.1.1.3, 7.1.1.4, 7.1.1.5, 7.1.1.6, 7.1.2.1, 7.1.2.2, 7.1.2.3, 7.1.2.4, 7.1.2.5, 7.1.2.6</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
           <t>7.SP.8c, Prep for 7.SP.C.8.A</t>
@@ -870,7 +898,7 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8c (CCSS-M), Prep for 7.SP.C.8.A (CCSS-M)</t>
+          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.4 (MN-2022), 7.1.1.5 (MN-2022), 7.1.1.6 (MN-2022), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2022), 7.1.2.4 (MN-2022), 7.1.2.5 (MN-2022), 7.1.2.6 (MN-2022), 7.4.3.1 (MN-2007), 7.4.3.2 (MN-2007), 7.SP.8c (CCSS-M), Prep for 7.SP.C.8.A (CCSS-M)</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -893,7 +921,11 @@
           <t>Fraction Addition</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3</t>
+        </is>
+      </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
           <t>5.NF.A.1, 7.SP.8c</t>
@@ -901,12 +933,12 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>5.NF.A.1 (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>5.NF.A.1 (CCSS-M), 7.3.5.1 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.5.7 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1251,11 @@
           <t>Multiplication of Rational Numbers</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr"/>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
           <t>7.NS.2a, 7.NS.A.2.A, 7.NS.A.2.C, 7.SP.8c</t>
@@ -1227,7 +1263,7 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.1 (MN-2022), 7.3.5.2 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -1250,7 +1286,11 @@
           <t>Multiplying of Mixed Numbers</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr"/>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
           <t>7.NS.2a, 7.NS.A.2.C, 7.SP.8c</t>
@@ -1258,7 +1298,7 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.NS.2a (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.1 (MN-2022), 7.3.5.2 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.NS.2a (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -1281,7 +1321,11 @@
           <t>Graphing Points on a Coordinate Plane</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr"/>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4, 7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
           <t>7.RP.2b, 7.RP.A.2.A, 7.RP.A.2.D, 7.SP.8c</t>
@@ -1289,7 +1333,7 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022), 7.2.4.1 (MN-2022), 7.2.4.2 (MN-2022), 7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.5.1 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.5.7 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.D (CCSS-M), 7.SP.8c (CCSS-M)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -1312,7 +1356,11 @@
           <t>Graphing Points on a Coordinate Plane</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr"/>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4, 7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
           <t>7.RP.2b, 7.RP.A.2.A, 7.RP.A.2.B</t>
@@ -1320,7 +1368,7 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022), 7.2.4.1 (MN-2022), 7.2.4.2 (MN-2022), 7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.1.1 (MN-2007), 7.3.1.2 (MN-2007), 7.3.5.1 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.5.7 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.A.2.A (CCSS-M), 7.RP.A.2.B (CCSS-M)</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -1462,7 +1510,11 @@
           <t>Adding and Subtracting Integers</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr"/>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
           <t>7.NS.1c, 7.NS.1d, 7.NS.A.1.C, 7.NS.A.1.D, 7.RP.2b</t>
@@ -1470,7 +1522,7 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.NS.1c (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.C (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.1 (MN-2022), 7.3.5.2 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.NS.1c (CCSS-M), 7.NS.1d (CCSS-M), 7.NS.A.1.C (CCSS-M), 7.NS.A.1.D (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -1528,7 +1580,11 @@
           <t>Multiplying Decimals</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr"/>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
           <t>7.NS.2a, 7.NS.A.2.A, 7.NS.A.2.C, 7.RP.2b</t>
@@ -1536,7 +1592,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.1 (MN-2022), 7.3.5.2 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.NS.2a (CCSS-M), 7.NS.A.2.A (CCSS-M), 7.NS.A.2.C (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -1629,7 +1685,11 @@
           <t>Dividing Decimals</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr"/>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
           <t>7.NS.A.2.C, 7.NS.A.3, 7.RP.2b</t>
@@ -1637,7 +1697,7 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.3.5.1 (MN-2022), 7.3.5.2 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.NS.A.2.C (CCSS-M), 7.NS.A.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -1953,7 +2013,11 @@
           <t>Using the Distributive Property</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr"/>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
           <t>7.EE.A.1, 7.RP.2b</t>
@@ -1961,7 +2025,7 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.EE.A.1 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2129,7 +2193,11 @@
           <t>Probability</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr"/>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>7.1.1.1, 7.1.1.2, 7.1.1.3, 7.1.1.4, 7.1.1.5, 7.1.1.6, 7.1.2.1, 7.1.2.2, 7.1.2.3, 7.1.2.4, 7.1.2.5, 7.1.2.6</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
           <t>7.RP.2b, 7.SP.7a</t>
@@ -2137,12 +2205,12 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>7.RP.2b (CCSS-M), 7.SP.7a (CCSS-M)</t>
+          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.4 (MN-2022), 7.1.1.5 (MN-2022), 7.1.1.6 (MN-2022), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2022), 7.1.2.4 (MN-2022), 7.1.2.5 (MN-2022), 7.1.2.6 (MN-2022), 7.RP.2b (CCSS-M), 7.SP.7a (CCSS-M)</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2403,11 @@
           <t>Describing Relationships Between Quantities</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr"/>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
           <t>7.EE.3, 7.RP.2b</t>
@@ -2343,7 +2415,7 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -2366,7 +2438,11 @@
           <t>Solving Word Problems</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr"/>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
           <t>7.EE.3, 7.RP.2b</t>
@@ -2374,7 +2450,7 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -2397,7 +2473,11 @@
           <t>Solving Word Problems</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr"/>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
           <t>7.EE.3, 7.RP.2b</t>
@@ -2405,7 +2485,7 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -2428,7 +2508,11 @@
           <t>Solving Word Problems with Variables</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr"/>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
           <t>7.EE.3, 7.RP.2b</t>
@@ -2436,7 +2520,7 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
@@ -2459,7 +2543,11 @@
           <t>Solving Word Problems with Variables</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr"/>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
           <t>7.EE.3, 7.RP.2b</t>
@@ -2467,7 +2555,7 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.EE.3 (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -2538,7 +2626,11 @@
           <t>Comparing Expressions with Variables</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr"/>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2</t>
+        </is>
+      </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
           <t>7.EE.4a, 7.EE.4b, 7.RP.2b</t>
@@ -2546,12 +2638,12 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.EE.4a (CCSS-M), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2696,11 @@
           <t>Solve one-variable inequalities</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr"/>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
           <t>7.EE.4b, 7.RP.2b</t>
@@ -2612,12 +2708,12 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.EE.4b (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2731,11 @@
           <t>Solving Equations</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr"/>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2</t>
+        </is>
+      </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
           <t>7.EE.4a, 7.RP.2b</t>
@@ -2643,12 +2743,12 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2766,11 @@
           <t>Solving Equations and the Distributive Property</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr"/>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2</t>
+        </is>
+      </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
           <t>7.EE.4a, 7.RP.2b</t>
@@ -2674,12 +2778,12 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2836,11 @@
           <t>Writing equations from Word Problems</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr"/>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
           <t>7.EE.3, 7.EE.4a, 7.RP.2b</t>
@@ -2740,7 +2848,7 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
@@ -2763,7 +2871,11 @@
           <t>Writing and Solving Equations</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr"/>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
           <t>7.EE.3, 7.EE.4a, 7.RP.2b</t>
@@ -2771,7 +2883,7 @@
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M)</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
@@ -2935,7 +3047,11 @@
           <t>Solving Problems Involving Percents</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.2, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4</t>
+        </is>
+      </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
           <t>7.NS.3, 7.RP.2b, 7.RP.3, see ebook</t>
@@ -2943,7 +3059,7 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.NS.3 (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.2.1 (MN-2007), 7.1.2.2 (MN-2007), 7.1.2.3 (MN-2007), 7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.5.1 (MN-2022), 7.3.5.2 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.NS.3 (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -3001,7 +3117,11 @@
           <t>Creating Integer Coefficients</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3</t>
+        </is>
+      </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
           <t>7.RP.2b, see ebook</t>
@@ -3009,12 +3129,12 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.3.5.1 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.5.7 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3152,11 @@
           <t>Creating Integer Coefficients Efficently</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr"/>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3</t>
+        </is>
+      </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
           <t>7.EE.2, 7.EE.4a, 7.RP.2b, see ebook</t>
@@ -3040,12 +3164,12 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>7.EE.2 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.3.5.1 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.5.7 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.EE.2 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3187,11 @@
           <t>Percent Increase and Decrease</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr"/>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.6, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
           <t>7.EE.3, 7.EE.4a, 7.RP.2b, 7.RP.3, see ebook</t>
@@ -3071,7 +3199,7 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.2.3.1 (MN-2007), 7.2.3.2 (MN-2007), 7.3.5.6 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.EE.3 (CCSS-M), 7.EE.4a (CCSS-M), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
@@ -3094,7 +3222,11 @@
           <t>Simple Interest</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr"/>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
           <t>7.RP.2b, 7.RP.3, see ebook</t>
@@ -3102,7 +3234,7 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.5.1 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.5.7 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
@@ -3160,7 +3292,11 @@
           <t>Solving Proportions</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr"/>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>7.3.5.1, 7.3.5.3, 7.3.5.4, 7.3.5.5, 7.3.5.6, 7.3.5.7, 7.3.6.1, 7.3.6.2, 7.3.6.3, 7.3.6.4, 7.3.6.5, 7.3.7.1, 7.3.7.2, 7.3.7.3</t>
+        </is>
+      </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
           <t>7.RP.2b, 7.RP.3, see ebook</t>
@@ -3168,7 +3304,7 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.1.1 (MN-2007), 7.2.1.2 (MN-2007), 7.2.2.1 (MN-2007), 7.2.2.2 (MN-2007), 7.3.5.1 (MN-2022), 7.3.5.3 (MN-2022), 7.3.5.4 (MN-2022), 7.3.5.5 (MN-2022), 7.3.5.6 (MN-2022), 7.3.5.7 (MN-2022), 7.3.6.1 (MN-2022), 7.3.6.2 (MN-2022), 7.3.6.3 (MN-2022), 7.3.6.4 (MN-2022), 7.3.6.5 (MN-2022), 7.3.7.1 (MN-2022), 7.3.7.2 (MN-2022), 7.3.7.3 (MN-2022), 7.RP.2b (CCSS-M), 7.RP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
@@ -3239,7 +3375,11 @@
           <t>Comparing Distributions</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr"/>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>7.1.1.1, 7.1.1.2, 7.1.1.3, 7.1.1.4, 7.1.1.5, 7.1.1.6, 7.1.2.1, 7.1.2.2, 7.1.2.3, 7.1.2.4, 7.1.2.5, 7.1.2.6</t>
+        </is>
+      </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
           <t>7.RP.2b, 7.SP.3, see ebook</t>
@@ -3247,7 +3387,7 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.3 (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.1.1.1 (MN-2022), 7.1.1.2 (MN-2022), 7.1.1.3 (MN-2022), 7.1.1.4 (MN-2022), 7.1.1.5 (MN-2022), 7.1.1.6 (MN-2022), 7.1.2.1 (MN-2022), 7.1.2.2 (MN-2022), 7.1.2.3 (MN-2022), 7.1.2.4 (MN-2022), 7.1.2.5 (MN-2022), 7.1.2.6 (MN-2022), 7.4.1.1 (MN-2007), 7.4.2.1 (MN-2007), 7.RP.2b (CCSS-M), 7.SP.3 (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
@@ -3477,7 +3617,11 @@
           <t>Circumference, Diameter, and Pi</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4</t>
+        </is>
+      </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
           <t>7.2.1, 7.G.4, 7.RP.2b, see ebook</t>
@@ -3485,7 +3629,7 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>7.2.1 (CCSS-M), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.4 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.1 (CCSS-M), 7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022), 7.2.4.1 (MN-2022), 7.2.4.2 (MN-2022), 7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.4 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -3508,7 +3652,11 @@
           <t>area of circles</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr"/>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4</t>
+        </is>
+      </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
           <t>7.RP.2b, see ebook</t>
@@ -3516,12 +3664,12 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022), 7.2.4.1 (MN-2022), 7.2.4.2 (MN-2022), 7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>ccss_lesson_guide, ccss_pdf_correlation</t>
+          <t>bridged_via_content, ccss_lesson_guide, ccss_pdf_correlation</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3687,11 @@
           <t>Area of Composite Shapes</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr"/>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4</t>
+        </is>
+      </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
           <t>7.G.4, 7.G.6, 7.RP.2b, see ebook</t>
@@ -3547,7 +3699,7 @@
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.4 (CCSS-M), 7.G.6 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022), 7.2.4.1 (MN-2022), 7.2.4.2 (MN-2022), 7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.2.1 (MN-2007), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.4 (CCSS-M), 7.G.6 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
@@ -3605,7 +3757,11 @@
           <t>Cross Sections</t>
         </is>
       </c>
-      <c r="D102" s="7" t="inlineStr"/>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4</t>
+        </is>
+      </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
           <t>7.2.1, 7.G.3, 7.RP.2b, see ebook</t>
@@ -3613,7 +3769,7 @@
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>7.2.1 (CCSS-M), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.3 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.1 (CCSS-M), 7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022), 7.2.4.1 (MN-2022), 7.2.4.2 (MN-2022), 7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.3 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
@@ -3636,7 +3792,11 @@
           <t>Volume of Prsms</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr"/>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4</t>
+        </is>
+      </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
           <t>7.G.6, 7.RP.2b, see ebook</t>
@@ -3644,7 +3804,7 @@
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.6 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022), 7.2.4.1 (MN-2022), 7.2.4.2 (MN-2022), 7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.6 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
@@ -3667,7 +3827,11 @@
           <t>Volume of Non-Rectangular Prisms</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr"/>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>7.2.3.1, 7.2.3.2, 7.2.3.3, 7.2.3.4, 7.2.4.1, 7.2.4.2, 7.2.4.3, 7.2.4.4</t>
+        </is>
+      </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
           <t>7.G.6, 7.RP.2b, see ebook</t>
@@ -3675,7 +3839,7 @@
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.6 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
+          <t>7.2.3.1 (MN-2022), 7.2.3.2 (MN-2022), 7.2.3.3 (MN-2022), 7.2.3.4 (MN-2022), 7.2.4.1 (MN-2022), 7.2.4.2 (MN-2022), 7.2.4.3 (MN-2022), 7.2.4.4 (MN-2022), 7.3.2.2 (MN-2007), 7.3.2.3 (MN-2007), 7.G.6 (CCSS-M), 7.RP.2b (CCSS-M), see ebook (CCSS-M)</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
